--- a/wisestar-client/public/templates/section-import-template.xlsx
+++ b/wisestar-client/public/templates/section-import-template.xlsx
@@ -413,16 +413,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>学科名</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>章节名</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>小节名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>排序(选填，数字越小越靠前)</t>
         </is>
@@ -431,21 +441,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>语文</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>识字与写字</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>拼音入门</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="D2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>字词辨析</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>100以内加减法</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>加法小站</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/wisestar-client/public/templates/section-import-template.xlsx
+++ b/wisestar-client/public/templates/section-import-template.xlsx
@@ -413,8 +413,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -434,7 +441,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>排序(选填，数字越小越靠前)</t>
+          <t>年级(选填)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>学期(选填)</t>
         </is>
       </c>
     </row>
@@ -454,8 +466,15 @@
           <t>拼音入门</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>1</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>一年级</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -474,8 +493,15 @@
           <t>加法小站</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>1</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>一年级</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
       </c>
     </row>
   </sheetData>
